--- a/output/graficos_nacionales/plot_nacional_e_rezjov_a_2024.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_rezjov_a_2024.xlsx
@@ -15175,7 +15175,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Rezago respecto a la población de 6 a 21 años</t>
+          <t>Por comunas</t>
         </is>
       </c>
     </row>

--- a/output/graficos_nacionales/plot_nacional_e_rezjov_a_2024.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_rezjov_a_2024.xlsx
@@ -416,7 +416,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -462,7 +462,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -508,7 +508,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5154,7 +5154,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -6902,7 +6902,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -7132,7 +7132,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -7270,7 +7270,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -7638,7 +7638,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -7730,7 +7730,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -8098,7 +8098,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -8282,7 +8282,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -8374,7 +8374,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -8650,7 +8650,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -8788,7 +8788,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -8972,7 +8972,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -9064,7 +9064,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -9432,7 +9432,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -9478,7 +9478,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -10490,7 +10490,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -10582,7 +10582,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -10996,7 +10996,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -11134,7 +11134,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -11318,7 +11318,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -11456,7 +11456,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -11640,7 +11640,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -11732,7 +11732,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -11916,7 +11916,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -12008,7 +12008,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -12100,7 +12100,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -12192,7 +12192,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -12284,7 +12284,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -12514,7 +12514,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -12560,7 +12560,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -12652,7 +12652,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -12790,7 +12790,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -12882,7 +12882,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -12928,7 +12928,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -13020,7 +13020,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -13066,7 +13066,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -13112,7 +13112,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -13250,7 +13250,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -13296,7 +13296,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -13342,7 +13342,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -13388,7 +13388,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -13434,7 +13434,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -13618,7 +13618,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -13756,7 +13756,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -13802,7 +13802,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -13848,7 +13848,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -13986,7 +13986,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -14032,7 +14032,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -14078,7 +14078,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -14124,7 +14124,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -14170,7 +14170,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -14216,7 +14216,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -14400,7 +14400,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -14446,7 +14446,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -14492,7 +14492,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -14538,7 +14538,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -14584,7 +14584,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -14722,7 +14722,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -14768,7 +14768,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -14814,7 +14814,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -14860,7 +14860,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -14906,7 +14906,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -14998,7 +14998,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -15044,7 +15044,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -15136,7 +15136,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -15182,7 +15182,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -15228,7 +15228,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -15320,7 +15320,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">

--- a/output/graficos_nacionales/plot_nacional_e_rezjov_a_2024.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_rezjov_a_2024.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="699">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="696">
   <si>
     <t xml:space="preserve">year</t>
   </si>
@@ -1300,15 +1300,6 @@
     <t xml:space="preserve">Punitaqui</t>
   </si>
   <si>
-    <t xml:space="preserve">Arica y Parinacota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arica</t>
-  </si>
-  <si>
     <t xml:space="preserve">4301</t>
   </si>
   <si>
@@ -2068,7 +2059,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 15:41</t>
+    <t xml:space="preserve">2026-09-07 12:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2480,7 +2471,7 @@
   <cols>
     <col min="1" max="1" width="10.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="11.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="20.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="15.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="12.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="22.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
@@ -8959,16 +8950,16 @@
         <v>2024</v>
       </c>
       <c r="B203" s="2" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C203" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="D203" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="D203" s="2" t="s">
+      <c r="E203" s="2" t="s">
         <v>428</v>
-      </c>
-      <c r="E203" s="2" t="s">
-        <v>429</v>
       </c>
       <c r="F203" s="2" t="s">
         <v>384</v>
@@ -8980,7 +8971,7 @@
         <v>15</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="J203" s="2" t="s">
         <v>15</v>
@@ -8997,10 +8988,10 @@
         <v>381</v>
       </c>
       <c r="D204" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="E204" s="2" t="s">
         <v>430</v>
-      </c>
-      <c r="E204" s="2" t="s">
-        <v>431</v>
       </c>
       <c r="F204" s="2" t="s">
         <v>384</v>
@@ -9012,7 +9003,7 @@
         <v>15</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="J204" s="2" t="s">
         <v>15</v>
@@ -9029,10 +9020,10 @@
         <v>381</v>
       </c>
       <c r="D205" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="E205" s="2" t="s">
         <v>432</v>
-      </c>
-      <c r="E205" s="2" t="s">
-        <v>433</v>
       </c>
       <c r="F205" s="2" t="s">
         <v>384</v>
@@ -9044,7 +9035,7 @@
         <v>15</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="J205" s="2" t="s">
         <v>15</v>
@@ -9055,16 +9046,16 @@
         <v>2024</v>
       </c>
       <c r="B206" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="D206" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="E206" s="2" t="s">
         <v>434</v>
-      </c>
-      <c r="E206" s="2" t="s">
-        <v>435</v>
       </c>
       <c r="F206" s="2" t="s">
         <v>384</v>
@@ -9076,7 +9067,7 @@
         <v>15</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="J206" s="2" t="s">
         <v>15</v>
@@ -9087,16 +9078,16 @@
         <v>2024</v>
       </c>
       <c r="B207" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="D207" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="E207" s="2" t="s">
         <v>436</v>
-      </c>
-      <c r="E207" s="2" t="s">
-        <v>437</v>
       </c>
       <c r="F207" s="2" t="s">
         <v>384</v>
@@ -9108,7 +9099,7 @@
         <v>15</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="J207" s="2" t="s">
         <v>15</v>
@@ -9119,16 +9110,16 @@
         <v>2024</v>
       </c>
       <c r="B208" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="D208" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="E208" s="2" t="s">
         <v>438</v>
-      </c>
-      <c r="E208" s="2" t="s">
-        <v>439</v>
       </c>
       <c r="F208" s="2" t="s">
         <v>384</v>
@@ -9140,7 +9131,7 @@
         <v>15</v>
       </c>
       <c r="I208" s="2" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="J208" s="2" t="s">
         <v>15</v>
@@ -9151,16 +9142,16 @@
         <v>2024</v>
       </c>
       <c r="B209" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="D209" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="E209" s="2" t="s">
         <v>440</v>
-      </c>
-      <c r="E209" s="2" t="s">
-        <v>441</v>
       </c>
       <c r="F209" s="2" t="s">
         <v>384</v>
@@ -9172,7 +9163,7 @@
         <v>15</v>
       </c>
       <c r="I209" s="2" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="J209" s="2" t="s">
         <v>15</v>
@@ -9189,10 +9180,10 @@
         <v>394</v>
       </c>
       <c r="D210" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="E210" s="2" t="s">
         <v>442</v>
-      </c>
-      <c r="E210" s="2" t="s">
-        <v>443</v>
       </c>
       <c r="F210" s="2" t="s">
         <v>384</v>
@@ -9215,16 +9206,16 @@
         <v>2024</v>
       </c>
       <c r="B211" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="D211" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="E211" s="2" t="s">
         <v>444</v>
-      </c>
-      <c r="E211" s="2" t="s">
-        <v>445</v>
       </c>
       <c r="F211" s="2" t="s">
         <v>384</v>
@@ -9236,7 +9227,7 @@
         <v>15</v>
       </c>
       <c r="I211" s="2" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="J211" s="2" t="s">
         <v>15</v>
@@ -9253,10 +9244,10 @@
         <v>386</v>
       </c>
       <c r="D212" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="E212" s="2" t="s">
         <v>446</v>
-      </c>
-      <c r="E212" s="2" t="s">
-        <v>447</v>
       </c>
       <c r="F212" s="2" t="s">
         <v>384</v>
@@ -9268,7 +9259,7 @@
         <v>15</v>
       </c>
       <c r="I212" s="2" t="n">
-        <v>1.27</v>
+        <v>1.12</v>
       </c>
       <c r="J212" s="2" t="s">
         <v>15</v>
@@ -9279,16 +9270,16 @@
         <v>2024</v>
       </c>
       <c r="B213" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="D213" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="E213" s="2" t="s">
         <v>448</v>
-      </c>
-      <c r="E213" s="2" t="s">
-        <v>449</v>
       </c>
       <c r="F213" s="2" t="s">
         <v>384</v>
@@ -9300,7 +9291,7 @@
         <v>15</v>
       </c>
       <c r="I213" s="2" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="J213" s="2" t="s">
         <v>15</v>
@@ -9317,10 +9308,10 @@
         <v>381</v>
       </c>
       <c r="D214" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="E214" s="2" t="s">
         <v>450</v>
-      </c>
-      <c r="E214" s="2" t="s">
-        <v>451</v>
       </c>
       <c r="F214" s="2" t="s">
         <v>384</v>
@@ -9332,7 +9323,7 @@
         <v>15</v>
       </c>
       <c r="I214" s="2" t="n">
-        <v>1.03</v>
+        <v>0.92</v>
       </c>
       <c r="J214" s="2" t="s">
         <v>15</v>
@@ -9343,16 +9334,16 @@
         <v>2024</v>
       </c>
       <c r="B215" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>381</v>
+        <v>394</v>
       </c>
       <c r="D215" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="E215" s="2" t="s">
         <v>452</v>
-      </c>
-      <c r="E215" s="2" t="s">
-        <v>453</v>
       </c>
       <c r="F215" s="2" t="s">
         <v>384</v>
@@ -9364,7 +9355,7 @@
         <v>15</v>
       </c>
       <c r="I215" s="2" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="J215" s="2" t="s">
         <v>15</v>
@@ -9375,16 +9366,16 @@
         <v>2024</v>
       </c>
       <c r="B216" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="D216" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="E216" s="2" t="s">
         <v>454</v>
-      </c>
-      <c r="E216" s="2" t="s">
-        <v>455</v>
       </c>
       <c r="F216" s="2" t="s">
         <v>384</v>
@@ -9396,7 +9387,7 @@
         <v>15</v>
       </c>
       <c r="I216" s="2" t="n">
-        <v>0.9</v>
+        <v>0.84</v>
       </c>
       <c r="J216" s="2" t="s">
         <v>15</v>
@@ -9407,16 +9398,16 @@
         <v>2024</v>
       </c>
       <c r="B217" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="D217" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="E217" s="2" t="s">
         <v>456</v>
-      </c>
-      <c r="E217" s="2" t="s">
-        <v>457</v>
       </c>
       <c r="F217" s="2" t="s">
         <v>384</v>
@@ -9445,10 +9436,10 @@
         <v>381</v>
       </c>
       <c r="D218" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="E218" s="2" t="s">
         <v>458</v>
-      </c>
-      <c r="E218" s="2" t="s">
-        <v>459</v>
       </c>
       <c r="F218" s="2" t="s">
         <v>384</v>
@@ -9460,7 +9451,7 @@
         <v>15</v>
       </c>
       <c r="I218" s="2" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="J218" s="2" t="s">
         <v>15</v>
@@ -9477,10 +9468,10 @@
         <v>381</v>
       </c>
       <c r="D219" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="E219" s="2" t="s">
         <v>460</v>
-      </c>
-      <c r="E219" s="2" t="s">
-        <v>461</v>
       </c>
       <c r="F219" s="2" t="s">
         <v>384</v>
@@ -9492,7 +9483,7 @@
         <v>15</v>
       </c>
       <c r="I219" s="2" t="n">
-        <v>0.83</v>
+        <v>0.66</v>
       </c>
       <c r="J219" s="2" t="s">
         <v>15</v>
@@ -9503,10 +9494,10 @@
         <v>2024</v>
       </c>
       <c r="B220" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>381</v>
+        <v>461</v>
       </c>
       <c r="D220" s="2" t="s">
         <v>462</v>
@@ -9515,16 +9506,16 @@
         <v>463</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>384</v>
+        <v>464</v>
       </c>
       <c r="G220" s="2" t="s">
-        <v>385</v>
+        <v>465</v>
       </c>
       <c r="H220" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I220" s="2" t="n">
-        <v>0.66</v>
+        <v>4.48</v>
       </c>
       <c r="J220" s="2" t="s">
         <v>15</v>
@@ -9535,28 +9526,28 @@
         <v>2024</v>
       </c>
       <c r="B221" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C221" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="D221" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="E221" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="F221" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="D221" s="2" t="s">
+      <c r="G221" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="E221" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="F221" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="G221" s="2" t="s">
-        <v>468</v>
-      </c>
       <c r="H221" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I221" s="2" t="n">
-        <v>4.48</v>
+        <v>3.43</v>
       </c>
       <c r="J221" s="2" t="s">
         <v>15</v>
@@ -9567,7 +9558,7 @@
         <v>2024</v>
       </c>
       <c r="B222" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C222" s="2" t="s">
         <v>469</v>
@@ -9579,16 +9570,16 @@
         <v>471</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G222" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H222" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I222" s="2" t="n">
-        <v>3.43</v>
+        <v>3.35</v>
       </c>
       <c r="J222" s="2" t="s">
         <v>15</v>
@@ -9599,28 +9590,28 @@
         <v>2024</v>
       </c>
       <c r="B223" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C223" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="D223" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="D223" s="2" t="s">
+      <c r="E223" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="E223" s="2" t="s">
-        <v>474</v>
-      </c>
       <c r="F223" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G223" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H223" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I223" s="2" t="n">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
       <c r="J223" s="2" t="s">
         <v>15</v>
@@ -9631,28 +9622,28 @@
         <v>2024</v>
       </c>
       <c r="B224" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C224" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="D224" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="E224" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="F224" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="D224" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="E224" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="F224" s="2" t="s">
-        <v>467</v>
-      </c>
       <c r="G224" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H224" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I224" s="2" t="n">
-        <v>3.31</v>
+        <v>3.26</v>
       </c>
       <c r="J224" s="2" t="s">
         <v>15</v>
@@ -9666,25 +9657,25 @@
         <v>10</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="D225" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="E225" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="E225" s="2" t="s">
-        <v>478</v>
-      </c>
       <c r="F225" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G225" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H225" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I225" s="2" t="n">
-        <v>3.26</v>
+        <v>3.19</v>
       </c>
       <c r="J225" s="2" t="s">
         <v>15</v>
@@ -9695,28 +9686,28 @@
         <v>2024</v>
       </c>
       <c r="B226" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C226" s="2" t="s">
         <v>469</v>
       </c>
       <c r="D226" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="E226" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="E226" s="2" t="s">
-        <v>480</v>
-      </c>
       <c r="F226" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G226" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H226" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I226" s="2" t="n">
-        <v>3.19</v>
+        <v>2.97</v>
       </c>
       <c r="J226" s="2" t="s">
         <v>15</v>
@@ -9727,28 +9718,28 @@
         <v>2024</v>
       </c>
       <c r="B227" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="D227" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="E227" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="E227" s="2" t="s">
-        <v>482</v>
-      </c>
       <c r="F227" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G227" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H227" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I227" s="2" t="n">
-        <v>2.97</v>
+        <v>2.73</v>
       </c>
       <c r="J227" s="2" t="s">
         <v>15</v>
@@ -9759,10 +9750,10 @@
         <v>2024</v>
       </c>
       <c r="B228" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>469</v>
+        <v>482</v>
       </c>
       <c r="D228" s="2" t="s">
         <v>483</v>
@@ -9771,16 +9762,16 @@
         <v>484</v>
       </c>
       <c r="F228" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G228" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H228" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I228" s="2" t="n">
-        <v>2.73</v>
+        <v>2.56</v>
       </c>
       <c r="J228" s="2" t="s">
         <v>15</v>
@@ -9791,28 +9782,28 @@
         <v>2024</v>
       </c>
       <c r="B229" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C229" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="D229" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="D229" s="2" t="s">
+      <c r="E229" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="E229" s="2" t="s">
-        <v>487</v>
-      </c>
       <c r="F229" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G229" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H229" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I229" s="2" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="J229" s="2" t="s">
         <v>15</v>
@@ -9823,28 +9814,28 @@
         <v>2024</v>
       </c>
       <c r="B230" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>469</v>
+        <v>482</v>
       </c>
       <c r="D230" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="E230" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="E230" s="2" t="s">
-        <v>489</v>
-      </c>
       <c r="F230" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G230" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H230" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I230" s="2" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="J230" s="2" t="s">
         <v>15</v>
@@ -9855,28 +9846,28 @@
         <v>2024</v>
       </c>
       <c r="B231" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>485</v>
+        <v>461</v>
       </c>
       <c r="D231" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="E231" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="E231" s="2" t="s">
-        <v>491</v>
-      </c>
       <c r="F231" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G231" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H231" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I231" s="2" t="n">
-        <v>2.53</v>
+        <v>2.47</v>
       </c>
       <c r="J231" s="2" t="s">
         <v>15</v>
@@ -9887,22 +9878,22 @@
         <v>2024</v>
       </c>
       <c r="B232" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C232" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="D232" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="E232" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="F232" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="D232" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="E232" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="F232" s="2" t="s">
-        <v>467</v>
-      </c>
       <c r="G232" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H232" s="2" t="s">
         <v>15</v>
@@ -9922,19 +9913,19 @@
         <v>10</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="D233" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="E233" s="2" t="s">
         <v>494</v>
       </c>
-      <c r="E233" s="2" t="s">
-        <v>495</v>
-      </c>
       <c r="F233" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G233" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H233" s="2" t="s">
         <v>15</v>
@@ -9951,28 +9942,28 @@
         <v>2024</v>
       </c>
       <c r="B234" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="D234" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="E234" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="E234" s="2" t="s">
-        <v>497</v>
-      </c>
       <c r="F234" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G234" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H234" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I234" s="2" t="n">
-        <v>2.47</v>
+        <v>2.43</v>
       </c>
       <c r="J234" s="2" t="s">
         <v>15</v>
@@ -9983,28 +9974,28 @@
         <v>2024</v>
       </c>
       <c r="B235" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C235" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="D235" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="E235" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="F235" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="D235" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="E235" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="F235" s="2" t="s">
-        <v>467</v>
-      </c>
       <c r="G235" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H235" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I235" s="2" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="J235" s="2" t="s">
         <v>15</v>
@@ -10018,25 +10009,25 @@
         <v>10</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="D236" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="E236" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="E236" s="2" t="s">
-        <v>501</v>
-      </c>
       <c r="F236" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G236" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H236" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I236" s="2" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="J236" s="2" t="s">
         <v>15</v>
@@ -10050,25 +10041,25 @@
         <v>10</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="D237" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="E237" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="E237" s="2" t="s">
-        <v>503</v>
-      </c>
       <c r="F237" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G237" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H237" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I237" s="2" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="J237" s="2" t="s">
         <v>15</v>
@@ -10079,28 +10070,28 @@
         <v>2024</v>
       </c>
       <c r="B238" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C238" s="2" t="s">
         <v>469</v>
       </c>
       <c r="D238" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="E238" s="2" t="s">
         <v>504</v>
       </c>
-      <c r="E238" s="2" t="s">
-        <v>505</v>
-      </c>
       <c r="F238" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G238" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H238" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I238" s="2" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="J238" s="2" t="s">
         <v>15</v>
@@ -10111,28 +10102,28 @@
         <v>2024</v>
       </c>
       <c r="B239" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="D239" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="E239" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="E239" s="2" t="s">
-        <v>507</v>
-      </c>
       <c r="F239" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G239" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H239" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I239" s="2" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="J239" s="2" t="s">
         <v>15</v>
@@ -10143,28 +10134,28 @@
         <v>2024</v>
       </c>
       <c r="B240" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C240" s="2" t="s">
         <v>469</v>
       </c>
       <c r="D240" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="E240" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="E240" s="2" t="s">
-        <v>509</v>
-      </c>
       <c r="F240" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G240" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H240" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I240" s="2" t="n">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="J240" s="2" t="s">
         <v>15</v>
@@ -10175,22 +10166,22 @@
         <v>2024</v>
       </c>
       <c r="B241" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="D241" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="E241" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="E241" s="2" t="s">
-        <v>511</v>
-      </c>
       <c r="F241" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G241" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H241" s="2" t="s">
         <v>15</v>
@@ -10210,25 +10201,25 @@
         <v>10</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="D242" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="E242" s="2" t="s">
         <v>512</v>
       </c>
-      <c r="E242" s="2" t="s">
-        <v>513</v>
-      </c>
       <c r="F242" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G242" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H242" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I242" s="2" t="n">
-        <v>2.33</v>
+        <v>2.26</v>
       </c>
       <c r="J242" s="2" t="s">
         <v>15</v>
@@ -10242,25 +10233,25 @@
         <v>10</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="D243" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="E243" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="E243" s="2" t="s">
-        <v>515</v>
-      </c>
       <c r="F243" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G243" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H243" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I243" s="2" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="J243" s="2" t="s">
         <v>15</v>
@@ -10271,28 +10262,28 @@
         <v>2024</v>
       </c>
       <c r="B244" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C244" s="2" t="s">
         <v>469</v>
       </c>
       <c r="D244" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="E244" s="2" t="s">
         <v>516</v>
       </c>
-      <c r="E244" s="2" t="s">
-        <v>517</v>
-      </c>
       <c r="F244" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G244" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H244" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I244" s="2" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="J244" s="2" t="s">
         <v>15</v>
@@ -10306,19 +10297,19 @@
         <v>9</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D245" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="E245" s="2" t="s">
         <v>518</v>
       </c>
-      <c r="E245" s="2" t="s">
-        <v>519</v>
-      </c>
       <c r="F245" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G245" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H245" s="2" t="s">
         <v>15</v>
@@ -10335,28 +10326,28 @@
         <v>2024</v>
       </c>
       <c r="B246" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>472</v>
+        <v>461</v>
       </c>
       <c r="D246" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="E246" s="2" t="s">
         <v>520</v>
       </c>
-      <c r="E246" s="2" t="s">
-        <v>521</v>
-      </c>
       <c r="F246" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G246" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H246" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I246" s="2" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="J246" s="2" t="s">
         <v>15</v>
@@ -10367,22 +10358,22 @@
         <v>2024</v>
       </c>
       <c r="B247" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C247" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="D247" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E247" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="F247" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="D247" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="E247" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="F247" s="2" t="s">
-        <v>467</v>
-      </c>
       <c r="G247" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H247" s="2" t="s">
         <v>15</v>
@@ -10399,28 +10390,28 @@
         <v>2024</v>
       </c>
       <c r="B248" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="D248" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="E248" s="2" t="s">
         <v>524</v>
       </c>
-      <c r="E248" s="2" t="s">
-        <v>525</v>
-      </c>
       <c r="F248" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G248" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H248" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I248" s="2" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="J248" s="2" t="s">
         <v>15</v>
@@ -10431,28 +10422,28 @@
         <v>2024</v>
       </c>
       <c r="B249" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="D249" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="E249" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="E249" s="2" t="s">
-        <v>527</v>
-      </c>
       <c r="F249" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G249" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H249" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I249" s="2" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="J249" s="2" t="s">
         <v>15</v>
@@ -10463,28 +10454,28 @@
         <v>2024</v>
       </c>
       <c r="B250" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C250" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="D250" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="E250" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="F250" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="D250" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="E250" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="F250" s="2" t="s">
-        <v>467</v>
-      </c>
       <c r="G250" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H250" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I250" s="2" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="J250" s="2" t="s">
         <v>15</v>
@@ -10495,28 +10486,28 @@
         <v>2024</v>
       </c>
       <c r="B251" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>472</v>
+        <v>461</v>
       </c>
       <c r="D251" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="E251" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="E251" s="2" t="s">
-        <v>531</v>
-      </c>
       <c r="F251" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G251" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H251" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I251" s="2" t="n">
-        <v>2.13</v>
+        <v>2.07</v>
       </c>
       <c r="J251" s="2" t="s">
         <v>15</v>
@@ -10527,28 +10518,28 @@
         <v>2024</v>
       </c>
       <c r="B252" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C252" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="D252" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="E252" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="F252" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="D252" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="E252" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="F252" s="2" t="s">
-        <v>467</v>
-      </c>
       <c r="G252" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H252" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I252" s="2" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="J252" s="2" t="s">
         <v>15</v>
@@ -10559,28 +10550,28 @@
         <v>2024</v>
       </c>
       <c r="B253" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C253" s="2" t="s">
         <v>469</v>
       </c>
       <c r="D253" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="E253" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="E253" s="2" t="s">
-        <v>535</v>
-      </c>
       <c r="F253" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G253" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H253" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I253" s="2" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="J253" s="2" t="s">
         <v>15</v>
@@ -10591,28 +10582,28 @@
         <v>2024</v>
       </c>
       <c r="B254" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="D254" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="E254" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="E254" s="2" t="s">
-        <v>537</v>
-      </c>
       <c r="F254" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G254" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H254" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I254" s="2" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="J254" s="2" t="s">
         <v>15</v>
@@ -10623,28 +10614,28 @@
         <v>2024</v>
       </c>
       <c r="B255" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="D255" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="E255" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="E255" s="2" t="s">
-        <v>539</v>
-      </c>
       <c r="F255" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G255" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H255" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I255" s="2" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="J255" s="2" t="s">
         <v>15</v>
@@ -10655,22 +10646,22 @@
         <v>2024</v>
       </c>
       <c r="B256" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C256" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="D256" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="E256" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="F256" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="D256" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="E256" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="F256" s="2" t="s">
-        <v>467</v>
-      </c>
       <c r="G256" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H256" s="2" t="s">
         <v>15</v>
@@ -10690,19 +10681,19 @@
         <v>14</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="D257" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="E257" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="E257" s="2" t="s">
-        <v>543</v>
-      </c>
       <c r="F257" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G257" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H257" s="2" t="s">
         <v>15</v>
@@ -10719,22 +10710,22 @@
         <v>2024</v>
       </c>
       <c r="B258" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>485</v>
+        <v>466</v>
       </c>
       <c r="D258" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="E258" s="2" t="s">
         <v>544</v>
       </c>
-      <c r="E258" s="2" t="s">
-        <v>545</v>
-      </c>
       <c r="F258" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G258" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H258" s="2" t="s">
         <v>15</v>
@@ -10751,28 +10742,28 @@
         <v>2024</v>
       </c>
       <c r="B259" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C259" s="2" t="s">
         <v>469</v>
       </c>
       <c r="D259" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="E259" s="2" t="s">
         <v>546</v>
       </c>
-      <c r="E259" s="2" t="s">
-        <v>547</v>
-      </c>
       <c r="F259" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G259" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H259" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I259" s="2" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="J259" s="2" t="s">
         <v>15</v>
@@ -10786,19 +10777,19 @@
         <v>9</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D260" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="E260" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="E260" s="2" t="s">
-        <v>549</v>
-      </c>
       <c r="F260" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G260" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H260" s="2" t="s">
         <v>15</v>
@@ -10815,22 +10806,22 @@
         <v>2024</v>
       </c>
       <c r="B261" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="D261" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="E261" s="2" t="s">
         <v>550</v>
       </c>
-      <c r="E261" s="2" t="s">
-        <v>551</v>
-      </c>
       <c r="F261" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G261" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H261" s="2" t="s">
         <v>15</v>
@@ -10850,19 +10841,19 @@
         <v>10</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="D262" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="E262" s="2" t="s">
         <v>552</v>
       </c>
-      <c r="E262" s="2" t="s">
-        <v>553</v>
-      </c>
       <c r="F262" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G262" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H262" s="2" t="s">
         <v>15</v>
@@ -10882,25 +10873,25 @@
         <v>10</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="D263" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="E263" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="E263" s="2" t="s">
-        <v>555</v>
-      </c>
       <c r="F263" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G263" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H263" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I263" s="2" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="J263" s="2" t="s">
         <v>15</v>
@@ -10911,28 +10902,28 @@
         <v>2024</v>
       </c>
       <c r="B264" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="D264" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="E264" s="2" t="s">
         <v>556</v>
       </c>
-      <c r="E264" s="2" t="s">
-        <v>557</v>
-      </c>
       <c r="F264" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G264" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H264" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I264" s="2" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="J264" s="2" t="s">
         <v>15</v>
@@ -10943,28 +10934,28 @@
         <v>2024</v>
       </c>
       <c r="B265" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C265" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="D265" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="E265" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="F265" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="D265" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="E265" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="F265" s="2" t="s">
-        <v>467</v>
-      </c>
       <c r="G265" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H265" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I265" s="2" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="J265" s="2" t="s">
         <v>15</v>
@@ -10975,28 +10966,28 @@
         <v>2024</v>
       </c>
       <c r="B266" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>472</v>
+        <v>482</v>
       </c>
       <c r="D266" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="E266" s="2" t="s">
         <v>560</v>
       </c>
-      <c r="E266" s="2" t="s">
-        <v>561</v>
-      </c>
       <c r="F266" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G266" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H266" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I266" s="2" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="J266" s="2" t="s">
         <v>15</v>
@@ -11007,22 +10998,22 @@
         <v>2024</v>
       </c>
       <c r="B267" s="2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>485</v>
+        <v>466</v>
       </c>
       <c r="D267" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="E267" s="2" t="s">
         <v>562</v>
       </c>
-      <c r="E267" s="2" t="s">
-        <v>563</v>
-      </c>
       <c r="F267" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G267" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H267" s="2" t="s">
         <v>15</v>
@@ -11039,28 +11030,28 @@
         <v>2024</v>
       </c>
       <c r="B268" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="D268" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="E268" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="E268" s="2" t="s">
-        <v>565</v>
-      </c>
       <c r="F268" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G268" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H268" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I268" s="2" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="J268" s="2" t="s">
         <v>15</v>
@@ -11071,22 +11062,22 @@
         <v>2024</v>
       </c>
       <c r="B269" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C269" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="D269" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="E269" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="F269" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="D269" s="2" t="s">
-        <v>566</v>
-      </c>
-      <c r="E269" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="F269" s="2" t="s">
-        <v>467</v>
-      </c>
       <c r="G269" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H269" s="2" t="s">
         <v>15</v>
@@ -11106,25 +11097,25 @@
         <v>9</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D270" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="E270" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="E270" s="2" t="s">
-        <v>569</v>
-      </c>
       <c r="F270" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G270" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H270" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I270" s="2" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="J270" s="2" t="s">
         <v>15</v>
@@ -11135,28 +11126,28 @@
         <v>2024</v>
       </c>
       <c r="B271" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="D271" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E271" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="E271" s="2" t="s">
-        <v>571</v>
-      </c>
       <c r="F271" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G271" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H271" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I271" s="2" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="J271" s="2" t="s">
         <v>15</v>
@@ -11167,28 +11158,28 @@
         <v>2024</v>
       </c>
       <c r="B272" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="D272" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="E272" s="2" t="s">
         <v>572</v>
       </c>
-      <c r="E272" s="2" t="s">
-        <v>573</v>
-      </c>
       <c r="F272" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G272" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H272" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I272" s="2" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="J272" s="2" t="s">
         <v>15</v>
@@ -11202,25 +11193,25 @@
         <v>8</v>
       </c>
       <c r="C273" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="D273" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="E273" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="F273" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="D273" s="2" t="s">
-        <v>574</v>
-      </c>
-      <c r="E273" s="2" t="s">
-        <v>575</v>
-      </c>
-      <c r="F273" s="2" t="s">
-        <v>467</v>
-      </c>
       <c r="G273" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H273" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I273" s="2" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="J273" s="2" t="s">
         <v>15</v>
@@ -11234,25 +11225,25 @@
         <v>8</v>
       </c>
       <c r="C274" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="D274" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="E274" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="F274" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="D274" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="E274" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="F274" s="2" t="s">
-        <v>467</v>
-      </c>
       <c r="G274" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H274" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I274" s="2" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="J274" s="2" t="s">
         <v>15</v>
@@ -11263,28 +11254,28 @@
         <v>2024</v>
       </c>
       <c r="B275" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C275" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="D275" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="E275" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="F275" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="D275" s="2" t="s">
-        <v>578</v>
-      </c>
-      <c r="E275" s="2" t="s">
-        <v>579</v>
-      </c>
-      <c r="F275" s="2" t="s">
-        <v>467</v>
-      </c>
       <c r="G275" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H275" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I275" s="2" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="J275" s="2" t="s">
         <v>15</v>
@@ -11298,19 +11289,19 @@
         <v>9</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D276" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="E276" s="2" t="s">
         <v>580</v>
       </c>
-      <c r="E276" s="2" t="s">
-        <v>581</v>
-      </c>
       <c r="F276" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G276" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H276" s="2" t="s">
         <v>15</v>
@@ -11330,25 +11321,25 @@
         <v>9</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D277" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="E277" s="2" t="s">
         <v>582</v>
       </c>
-      <c r="E277" s="2" t="s">
-        <v>583</v>
-      </c>
       <c r="F277" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G277" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H277" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I277" s="2" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="J277" s="2" t="s">
         <v>15</v>
@@ -11362,25 +11353,25 @@
         <v>9</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D278" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="E278" s="2" t="s">
         <v>584</v>
       </c>
-      <c r="E278" s="2" t="s">
-        <v>585</v>
-      </c>
       <c r="F278" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G278" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H278" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I278" s="2" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="J278" s="2" t="s">
         <v>15</v>
@@ -11391,28 +11382,28 @@
         <v>2024</v>
       </c>
       <c r="B279" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="D279" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="E279" s="2" t="s">
         <v>586</v>
       </c>
-      <c r="E279" s="2" t="s">
-        <v>587</v>
-      </c>
       <c r="F279" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G279" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H279" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I279" s="2" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="J279" s="2" t="s">
         <v>15</v>
@@ -11423,28 +11414,28 @@
         <v>2024</v>
       </c>
       <c r="B280" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="D280" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="E280" s="2" t="s">
         <v>588</v>
       </c>
-      <c r="E280" s="2" t="s">
-        <v>589</v>
-      </c>
       <c r="F280" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G280" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H280" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I280" s="2" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="J280" s="2" t="s">
         <v>15</v>
@@ -11458,19 +11449,19 @@
         <v>8</v>
       </c>
       <c r="C281" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="D281" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="E281" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="F281" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="D281" s="2" t="s">
-        <v>590</v>
-      </c>
-      <c r="E281" s="2" t="s">
-        <v>591</v>
-      </c>
-      <c r="F281" s="2" t="s">
-        <v>467</v>
-      </c>
       <c r="G281" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H281" s="2" t="s">
         <v>15</v>
@@ -11487,28 +11478,28 @@
         <v>2024</v>
       </c>
       <c r="B282" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C282" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="D282" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="E282" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="F282" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="D282" s="2" t="s">
-        <v>592</v>
-      </c>
-      <c r="E282" s="2" t="s">
-        <v>593</v>
-      </c>
-      <c r="F282" s="2" t="s">
-        <v>467</v>
-      </c>
       <c r="G282" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H282" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I282" s="2" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="J282" s="2" t="s">
         <v>15</v>
@@ -11519,28 +11510,28 @@
         <v>2024</v>
       </c>
       <c r="B283" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>472</v>
+        <v>461</v>
       </c>
       <c r="D283" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="E283" s="2" t="s">
         <v>594</v>
       </c>
-      <c r="E283" s="2" t="s">
-        <v>595</v>
-      </c>
       <c r="F283" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G283" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H283" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I283" s="2" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="J283" s="2" t="s">
         <v>15</v>
@@ -11554,25 +11545,25 @@
         <v>8</v>
       </c>
       <c r="C284" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="D284" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="E284" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="F284" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="D284" s="2" t="s">
-        <v>596</v>
-      </c>
-      <c r="E284" s="2" t="s">
-        <v>597</v>
-      </c>
-      <c r="F284" s="2" t="s">
-        <v>467</v>
-      </c>
       <c r="G284" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H284" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I284" s="2" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="J284" s="2" t="s">
         <v>15</v>
@@ -11583,28 +11574,28 @@
         <v>2024</v>
       </c>
       <c r="B285" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C285" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="D285" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="E285" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="F285" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="D285" s="2" t="s">
-        <v>598</v>
-      </c>
-      <c r="E285" s="2" t="s">
-        <v>599</v>
-      </c>
-      <c r="F285" s="2" t="s">
-        <v>467</v>
-      </c>
       <c r="G285" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H285" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I285" s="2" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="J285" s="2" t="s">
         <v>15</v>
@@ -11618,25 +11609,25 @@
         <v>10</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="D286" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="E286" s="2" t="s">
         <v>600</v>
       </c>
-      <c r="E286" s="2" t="s">
-        <v>601</v>
-      </c>
       <c r="F286" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G286" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H286" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I286" s="2" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="J286" s="2" t="s">
         <v>15</v>
@@ -11647,28 +11638,28 @@
         <v>2024</v>
       </c>
       <c r="B287" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="D287" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="E287" s="2" t="s">
         <v>602</v>
       </c>
-      <c r="E287" s="2" t="s">
-        <v>603</v>
-      </c>
       <c r="F287" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G287" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H287" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I287" s="2" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="J287" s="2" t="s">
         <v>15</v>
@@ -11679,28 +11670,28 @@
         <v>2024</v>
       </c>
       <c r="B288" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C288" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="D288" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="E288" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="F288" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="D288" s="2" t="s">
-        <v>604</v>
-      </c>
-      <c r="E288" s="2" t="s">
-        <v>605</v>
-      </c>
-      <c r="F288" s="2" t="s">
-        <v>467</v>
-      </c>
       <c r="G288" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H288" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I288" s="2" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="J288" s="2" t="s">
         <v>15</v>
@@ -11711,28 +11702,28 @@
         <v>2024</v>
       </c>
       <c r="B289" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>485</v>
+        <v>461</v>
       </c>
       <c r="D289" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="E289" s="2" t="s">
         <v>606</v>
       </c>
-      <c r="E289" s="2" t="s">
-        <v>607</v>
-      </c>
       <c r="F289" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G289" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H289" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I289" s="2" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="J289" s="2" t="s">
         <v>15</v>
@@ -11743,22 +11734,22 @@
         <v>2024</v>
       </c>
       <c r="B290" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C290" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="D290" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="E290" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="F290" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="D290" s="2" t="s">
-        <v>608</v>
-      </c>
-      <c r="E290" s="2" t="s">
-        <v>609</v>
-      </c>
-      <c r="F290" s="2" t="s">
-        <v>467</v>
-      </c>
       <c r="G290" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H290" s="2" t="s">
         <v>15</v>
@@ -11778,19 +11769,19 @@
         <v>9</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D291" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="E291" s="2" t="s">
         <v>610</v>
       </c>
-      <c r="E291" s="2" t="s">
-        <v>611</v>
-      </c>
       <c r="F291" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G291" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H291" s="2" t="s">
         <v>15</v>
@@ -11807,28 +11798,28 @@
         <v>2024</v>
       </c>
       <c r="B292" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>472</v>
+        <v>461</v>
       </c>
       <c r="D292" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="E292" s="2" t="s">
         <v>612</v>
       </c>
-      <c r="E292" s="2" t="s">
-        <v>613</v>
-      </c>
       <c r="F292" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G292" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H292" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I292" s="2" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="J292" s="2" t="s">
         <v>15</v>
@@ -11842,19 +11833,19 @@
         <v>8</v>
       </c>
       <c r="C293" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="D293" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="E293" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="F293" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="D293" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="E293" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="F293" s="2" t="s">
-        <v>467</v>
-      </c>
       <c r="G293" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H293" s="2" t="s">
         <v>15</v>
@@ -11871,28 +11862,28 @@
         <v>2024</v>
       </c>
       <c r="B294" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C294" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="D294" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="E294" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="F294" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="D294" s="2" t="s">
-        <v>616</v>
-      </c>
-      <c r="E294" s="2" t="s">
-        <v>617</v>
-      </c>
-      <c r="F294" s="2" t="s">
-        <v>467</v>
-      </c>
       <c r="G294" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H294" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I294" s="2" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="J294" s="2" t="s">
         <v>15</v>
@@ -11906,19 +11897,19 @@
         <v>9</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D295" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="E295" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="E295" s="2" t="s">
-        <v>619</v>
-      </c>
       <c r="F295" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G295" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H295" s="2" t="s">
         <v>15</v>
@@ -11935,28 +11926,28 @@
         <v>2024</v>
       </c>
       <c r="B296" s="2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>472</v>
+        <v>482</v>
       </c>
       <c r="D296" s="2" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="E296" s="2" t="s">
-        <v>621</v>
+        <v>466</v>
       </c>
       <c r="F296" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G296" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H296" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I296" s="2" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="J296" s="2" t="s">
         <v>15</v>
@@ -11967,28 +11958,28 @@
         <v>2024</v>
       </c>
       <c r="B297" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>485</v>
+        <v>461</v>
       </c>
       <c r="D297" s="2" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="E297" s="2" t="s">
-        <v>469</v>
+        <v>621</v>
       </c>
       <c r="F297" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G297" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H297" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I297" s="2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="J297" s="2" t="s">
         <v>15</v>
@@ -12002,25 +11993,25 @@
         <v>8</v>
       </c>
       <c r="C298" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="D298" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="E298" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="F298" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="D298" s="2" t="s">
-        <v>623</v>
-      </c>
-      <c r="E298" s="2" t="s">
-        <v>624</v>
-      </c>
-      <c r="F298" s="2" t="s">
-        <v>467</v>
-      </c>
       <c r="G298" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H298" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I298" s="2" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="J298" s="2" t="s">
         <v>15</v>
@@ -12034,19 +12025,19 @@
         <v>8</v>
       </c>
       <c r="C299" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="D299" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="E299" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="F299" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="D299" s="2" t="s">
-        <v>625</v>
-      </c>
-      <c r="E299" s="2" t="s">
-        <v>626</v>
-      </c>
-      <c r="F299" s="2" t="s">
-        <v>467</v>
-      </c>
       <c r="G299" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H299" s="2" t="s">
         <v>15</v>
@@ -12063,22 +12054,22 @@
         <v>2024</v>
       </c>
       <c r="B300" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C300" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="D300" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="E300" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="F300" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="D300" s="2" t="s">
-        <v>627</v>
-      </c>
-      <c r="E300" s="2" t="s">
-        <v>628</v>
-      </c>
-      <c r="F300" s="2" t="s">
-        <v>467</v>
-      </c>
       <c r="G300" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H300" s="2" t="s">
         <v>15</v>
@@ -12095,28 +12086,28 @@
         <v>2024</v>
       </c>
       <c r="B301" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>485</v>
+        <v>469</v>
       </c>
       <c r="D301" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="E301" s="2" t="s">
         <v>629</v>
       </c>
-      <c r="E301" s="2" t="s">
-        <v>630</v>
-      </c>
       <c r="F301" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G301" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H301" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I301" s="2" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="J301" s="2" t="s">
         <v>15</v>
@@ -12127,28 +12118,28 @@
         <v>2024</v>
       </c>
       <c r="B302" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>472</v>
+        <v>461</v>
       </c>
       <c r="D302" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="E302" s="2" t="s">
         <v>631</v>
       </c>
-      <c r="E302" s="2" t="s">
-        <v>632</v>
-      </c>
       <c r="F302" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G302" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H302" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I302" s="2" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="J302" s="2" t="s">
         <v>15</v>
@@ -12159,22 +12150,22 @@
         <v>2024</v>
       </c>
       <c r="B303" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C303" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="D303" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="E303" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="F303" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="D303" s="2" t="s">
-        <v>633</v>
-      </c>
-      <c r="E303" s="2" t="s">
-        <v>634</v>
-      </c>
-      <c r="F303" s="2" t="s">
-        <v>467</v>
-      </c>
       <c r="G303" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H303" s="2" t="s">
         <v>15</v>
@@ -12194,25 +12185,25 @@
         <v>10</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="D304" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="E304" s="2" t="s">
         <v>635</v>
       </c>
-      <c r="E304" s="2" t="s">
-        <v>636</v>
-      </c>
       <c r="F304" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G304" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H304" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I304" s="2" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="J304" s="2" t="s">
         <v>15</v>
@@ -12223,28 +12214,28 @@
         <v>2024</v>
       </c>
       <c r="B305" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C305" s="2" t="s">
         <v>469</v>
       </c>
       <c r="D305" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="E305" s="2" t="s">
         <v>637</v>
       </c>
-      <c r="E305" s="2" t="s">
-        <v>638</v>
-      </c>
       <c r="F305" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G305" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H305" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I305" s="2" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="J305" s="2" t="s">
         <v>15</v>
@@ -12255,28 +12246,28 @@
         <v>2024</v>
       </c>
       <c r="B306" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>472</v>
+        <v>461</v>
       </c>
       <c r="D306" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="E306" s="2" t="s">
         <v>639</v>
       </c>
-      <c r="E306" s="2" t="s">
-        <v>640</v>
-      </c>
       <c r="F306" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G306" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H306" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I306" s="2" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="J306" s="2" t="s">
         <v>15</v>
@@ -12287,22 +12278,22 @@
         <v>2024</v>
       </c>
       <c r="B307" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C307" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="D307" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="E307" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="F307" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="D307" s="2" t="s">
-        <v>641</v>
-      </c>
-      <c r="E307" s="2" t="s">
-        <v>642</v>
-      </c>
-      <c r="F307" s="2" t="s">
-        <v>467</v>
-      </c>
       <c r="G307" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H307" s="2" t="s">
         <v>15</v>
@@ -12319,28 +12310,28 @@
         <v>2024</v>
       </c>
       <c r="B308" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>472</v>
+        <v>461</v>
       </c>
       <c r="D308" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="E308" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="E308" s="2" t="s">
-        <v>644</v>
-      </c>
       <c r="F308" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G308" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H308" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I308" s="2" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="J308" s="2" t="s">
         <v>15</v>
@@ -12354,19 +12345,19 @@
         <v>8</v>
       </c>
       <c r="C309" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="D309" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="E309" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="F309" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="D309" s="2" t="s">
-        <v>645</v>
-      </c>
-      <c r="E309" s="2" t="s">
-        <v>646</v>
-      </c>
-      <c r="F309" s="2" t="s">
-        <v>467</v>
-      </c>
       <c r="G309" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H309" s="2" t="s">
         <v>15</v>
@@ -12386,25 +12377,25 @@
         <v>8</v>
       </c>
       <c r="C310" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="D310" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="E310" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="F310" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="D310" s="2" t="s">
-        <v>647</v>
-      </c>
-      <c r="E310" s="2" t="s">
-        <v>648</v>
-      </c>
-      <c r="F310" s="2" t="s">
-        <v>467</v>
-      </c>
       <c r="G310" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H310" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I310" s="2" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="J310" s="2" t="s">
         <v>15</v>
@@ -12415,22 +12406,22 @@
         <v>2024</v>
       </c>
       <c r="B311" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C311" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="D311" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="E311" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="F311" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="D311" s="2" t="s">
-        <v>649</v>
-      </c>
-      <c r="E311" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="F311" s="2" t="s">
-        <v>467</v>
-      </c>
       <c r="G311" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H311" s="2" t="s">
         <v>15</v>
@@ -12447,22 +12438,22 @@
         <v>2024</v>
       </c>
       <c r="B312" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="D312" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="E312" s="2" t="s">
         <v>651</v>
       </c>
-      <c r="E312" s="2" t="s">
-        <v>652</v>
-      </c>
       <c r="F312" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G312" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H312" s="2" t="s">
         <v>15</v>
@@ -12482,19 +12473,19 @@
         <v>10</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="D313" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="E313" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="E313" s="2" t="s">
-        <v>654</v>
-      </c>
       <c r="F313" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G313" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H313" s="2" t="s">
         <v>15</v>
@@ -12511,28 +12502,28 @@
         <v>2024</v>
       </c>
       <c r="B314" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>469</v>
+        <v>482</v>
       </c>
       <c r="D314" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="E314" s="2" t="s">
         <v>655</v>
       </c>
-      <c r="E314" s="2" t="s">
-        <v>656</v>
-      </c>
       <c r="F314" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G314" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H314" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I314" s="2" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="J314" s="2" t="s">
         <v>15</v>
@@ -12543,28 +12534,28 @@
         <v>2024</v>
       </c>
       <c r="B315" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>485</v>
+        <v>461</v>
       </c>
       <c r="D315" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="E315" s="2" t="s">
         <v>657</v>
       </c>
-      <c r="E315" s="2" t="s">
-        <v>658</v>
-      </c>
       <c r="F315" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G315" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H315" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I315" s="2" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="J315" s="2" t="s">
         <v>15</v>
@@ -12575,22 +12566,22 @@
         <v>2024</v>
       </c>
       <c r="B316" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C316" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="D316" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="E316" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="F316" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="D316" s="2" t="s">
-        <v>659</v>
-      </c>
-      <c r="E316" s="2" t="s">
-        <v>660</v>
-      </c>
-      <c r="F316" s="2" t="s">
-        <v>467</v>
-      </c>
       <c r="G316" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H316" s="2" t="s">
         <v>15</v>
@@ -12610,25 +12601,25 @@
         <v>9</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D317" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="E317" s="2" t="s">
         <v>661</v>
       </c>
-      <c r="E317" s="2" t="s">
-        <v>662</v>
-      </c>
       <c r="F317" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G317" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H317" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I317" s="2" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="J317" s="2" t="s">
         <v>15</v>
@@ -12639,28 +12630,28 @@
         <v>2024</v>
       </c>
       <c r="B318" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>472</v>
+        <v>461</v>
       </c>
       <c r="D318" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="E318" s="2" t="s">
         <v>663</v>
       </c>
-      <c r="E318" s="2" t="s">
-        <v>664</v>
-      </c>
       <c r="F318" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G318" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H318" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I318" s="2" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="J318" s="2" t="s">
         <v>15</v>
@@ -12671,28 +12662,28 @@
         <v>2024</v>
       </c>
       <c r="B319" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C319" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="D319" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="E319" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="F319" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="D319" s="2" t="s">
-        <v>665</v>
-      </c>
-      <c r="E319" s="2" t="s">
-        <v>666</v>
-      </c>
-      <c r="F319" s="2" t="s">
-        <v>467</v>
-      </c>
       <c r="G319" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H319" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I319" s="2" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="J319" s="2" t="s">
         <v>15</v>
@@ -12703,28 +12694,28 @@
         <v>2024</v>
       </c>
       <c r="B320" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>485</v>
+        <v>469</v>
       </c>
       <c r="D320" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="E320" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="E320" s="2" t="s">
-        <v>668</v>
-      </c>
       <c r="F320" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G320" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H320" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I320" s="2" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="J320" s="2" t="s">
         <v>15</v>
@@ -12735,28 +12726,28 @@
         <v>2024</v>
       </c>
       <c r="B321" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>472</v>
+        <v>461</v>
       </c>
       <c r="D321" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="E321" s="2" t="s">
         <v>669</v>
       </c>
-      <c r="E321" s="2" t="s">
-        <v>670</v>
-      </c>
       <c r="F321" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G321" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H321" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I321" s="2" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="J321" s="2" t="s">
         <v>15</v>
@@ -12767,28 +12758,28 @@
         <v>2024</v>
       </c>
       <c r="B322" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C322" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="D322" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="E322" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="F322" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="D322" s="2" t="s">
-        <v>671</v>
-      </c>
-      <c r="E322" s="2" t="s">
-        <v>672</v>
-      </c>
-      <c r="F322" s="2" t="s">
-        <v>467</v>
-      </c>
       <c r="G322" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H322" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I322" s="2" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="J322" s="2" t="s">
         <v>15</v>
@@ -12799,28 +12790,28 @@
         <v>2024</v>
       </c>
       <c r="B323" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>472</v>
+        <v>461</v>
       </c>
       <c r="D323" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="E323" s="2" t="s">
         <v>673</v>
       </c>
-      <c r="E323" s="2" t="s">
-        <v>674</v>
-      </c>
       <c r="F323" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G323" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H323" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I323" s="2" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="J323" s="2" t="s">
         <v>15</v>
@@ -12831,22 +12822,22 @@
         <v>2024</v>
       </c>
       <c r="B324" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C324" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="D324" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="E324" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="F324" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="D324" s="2" t="s">
-        <v>675</v>
-      </c>
-      <c r="E324" s="2" t="s">
-        <v>676</v>
-      </c>
-      <c r="F324" s="2" t="s">
-        <v>467</v>
-      </c>
       <c r="G324" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H324" s="2" t="s">
         <v>15</v>
@@ -12863,67 +12854,35 @@
         <v>2024</v>
       </c>
       <c r="B325" s="2" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>485</v>
+        <v>469</v>
       </c>
       <c r="D325" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="E325" s="2" t="s">
         <v>677</v>
       </c>
-      <c r="E325" s="2" t="s">
-        <v>678</v>
-      </c>
       <c r="F325" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G325" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="H325" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I325" s="2" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="J325" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="326">
-      <c r="A326" s="2" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B326" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="C326" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="D326" s="2" t="s">
-        <v>679</v>
-      </c>
-      <c r="E326" s="2" t="s">
-        <v>680</v>
-      </c>
-      <c r="F326" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="G326" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="H326" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I326" s="2" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="J326" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J326"/>
+  <autoFilter ref="A1:J325"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -12940,7 +12899,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>8</v>
@@ -12948,50 +12907,50 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
     </row>
   </sheetData>
@@ -13013,21 +12972,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>15</v>
@@ -13036,7 +12995,7 @@
         <v>2024</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_nacionales/plot_nacional_e_rezjov_a_2024.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_rezjov_a_2024.xlsx
@@ -2059,7 +2059,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 12:58</t>
+    <t xml:space="preserve">2026-09-08 10:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
